--- a/Design-Files/FMM-v1.0/BOM/eSpark-BOM-FMM-v1.0.xlsx
+++ b/Design-Files/FMM-v1.0/BOM/eSpark-BOM-FMM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="404">
   <si>
     <t>#</t>
   </si>
@@ -42,9 +42,6 @@
     <t>TVS Diode</t>
   </si>
   <si>
-    <t>Fuse Holder</t>
-  </si>
-  <si>
     <t>Connector</t>
   </si>
   <si>
@@ -288,9 +285,6 @@
     <t>DIODE ZENER 3.3V 200MW SOD323F</t>
   </si>
   <si>
-    <t>TVS DIODE 33VWM 53.3VC SMA</t>
-  </si>
-  <si>
     <t>DIODE SCHOTTKY 20V 500MA SOD123</t>
   </si>
   <si>
@@ -306,9 +300,6 @@
     <t>TVS DIODE 3.3VWM 11.5VC MICROSMP</t>
   </si>
   <si>
-    <t>FUSE HOLDER BLADE 80V PCB</t>
-  </si>
-  <si>
     <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
@@ -480,9 +471,6 @@
     <t>SOD323F</t>
   </si>
   <si>
-    <t>SMA</t>
-  </si>
-  <si>
     <t>SOD-123</t>
   </si>
   <si>
@@ -498,9 +486,6 @@
     <t>MicroSMP</t>
   </si>
   <si>
-    <t>178.6165.0002</t>
-  </si>
-  <si>
     <t>SRP1265A-8R2M</t>
   </si>
   <si>
@@ -618,9 +603,6 @@
     <t>MM3Z3V3B</t>
   </si>
   <si>
-    <t>SMAJ33AQ-13-F</t>
-  </si>
-  <si>
     <t>MBR0520LT1G</t>
   </si>
   <si>
@@ -789,9 +771,6 @@
     <t>Bourns</t>
   </si>
   <si>
-    <t>Littelfuse Wickmann</t>
-  </si>
-  <si>
     <t>BOOMELE</t>
   </si>
   <si>
@@ -1029,9 +1008,6 @@
     <t>RC0603FR-0722RL</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>R14</t>
   </si>
   <si>
@@ -1224,7 +1200,37 @@
     <t>KHB65-37(11)-28-A/3</t>
   </si>
   <si>
-    <t>Custom Supplier Quote Required</t>
+    <t>TVS DIODE 30VWM 48.4VC SMC</t>
+  </si>
+  <si>
+    <t>SMC</t>
+  </si>
+  <si>
+    <t>3.0SMCJ30AQ-13</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>16V 1A 100A 1.8A 1206 Resettable Fuses ROHS</t>
+  </si>
+  <si>
+    <t>Fuse 1206 (3216 Metric)</t>
+  </si>
+  <si>
+    <t>BSMD1206-100-16V</t>
+  </si>
+  <si>
+    <t>BHFUSE</t>
+  </si>
+  <si>
+    <t>DJ7391-1.5/2.8-11 automotive male 39 pin pcb connector ecu connector</t>
+  </si>
+  <si>
+    <t>Alibaba</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1607,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1701,6 +1707,18 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1728,16 +1746,10 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2059,13 +2071,13 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2077,40 +2089,40 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>314</v>
-      </c>
       <c r="O2" s="5" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2123,22 +2135,22 @@
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J3" s="7">
         <v>9</v>
@@ -2148,7 +2160,7 @@
         <v>45</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M3" s="14">
         <v>0.124</v>
@@ -2169,22 +2181,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J4" s="9">
         <v>31</v>
@@ -2194,7 +2206,7 @@
         <v>155</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M4" s="14">
         <v>1.9400000000000001E-2</v>
@@ -2215,22 +2227,22 @@
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -2240,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M5" s="14">
         <v>0.92100000000000004</v>
@@ -2261,22 +2273,22 @@
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -2286,7 +2298,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M6" s="14">
         <v>1.0389999999999999</v>
@@ -2307,22 +2319,22 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -2332,7 +2344,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M7" s="14">
         <v>0.22</v>
@@ -2353,22 +2365,22 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -2378,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M8" s="14">
         <v>0.1</v>
@@ -2399,22 +2411,22 @@
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -2424,7 +2436,7 @@
         <v>5</v>
       </c>
       <c r="L9" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M9" s="14">
         <v>0.1</v>
@@ -2445,22 +2457,22 @@
         <v>2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -2470,7 +2482,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M10" s="14">
         <v>0.1</v>
@@ -2491,22 +2503,22 @@
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
@@ -2516,7 +2528,7 @@
         <v>5</v>
       </c>
       <c r="L11" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M11" s="14">
         <v>0.1</v>
@@ -2537,22 +2549,22 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="J12" s="9">
         <v>3</v>
@@ -2562,7 +2574,7 @@
         <v>15</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M12" s="14">
         <v>0.22600000000000001</v>
@@ -2583,22 +2595,22 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -2608,7 +2620,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M13" s="14">
         <v>0.73699999999999999</v>
@@ -2629,22 +2641,22 @@
         <v>2</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -2654,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M14" s="14">
         <v>0.22</v>
@@ -2675,22 +2687,22 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="J15" s="7">
         <v>7</v>
@@ -2700,7 +2712,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M15" s="14">
         <v>0.26</v>
@@ -2721,22 +2733,22 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -2746,7 +2758,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M16" s="14">
         <v>0.45</v>
@@ -2767,22 +2779,22 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="J17" s="7">
         <v>2</v>
@@ -2792,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M17" s="14">
         <v>0.11899999999999999</v>
@@ -2813,22 +2825,22 @@
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -2838,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="L18" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M18" s="14">
         <v>0.48</v>
@@ -2859,22 +2871,22 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J19" s="7">
         <v>12</v>
@@ -2884,7 +2896,7 @@
         <v>60</v>
       </c>
       <c r="L19" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M19" s="14">
         <v>0.1</v>
@@ -2905,22 +2917,22 @@
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J20" s="9">
         <v>4</v>
@@ -2930,7 +2942,7 @@
         <v>20</v>
       </c>
       <c r="L20" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M20" s="14">
         <v>0.1</v>
@@ -2951,22 +2963,22 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>346</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>354</v>
       </c>
       <c r="J21" s="7">
         <v>4</v>
@@ -2976,7 +2988,7 @@
         <v>20</v>
       </c>
       <c r="L21" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M21" s="14">
         <v>0.1</v>
@@ -2997,22 +3009,22 @@
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J22" s="7">
         <v>1</v>
@@ -3022,7 +3034,7 @@
         <v>5</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M22" s="14">
         <v>2.96</v>
@@ -3043,22 +3055,22 @@
         <v>3</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J23" s="9">
         <v>1</v>
@@ -3068,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M23" s="14">
         <v>0.91</v>
@@ -3089,22 +3101,22 @@
         <v>3</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J24" s="7">
         <v>1</v>
@@ -3114,7 +3126,7 @@
         <v>5</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M24" s="14">
         <v>0.21</v>
@@ -3134,25 +3146,25 @@
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>250</v>
+      <c r="D25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="J25" s="9">
+        <v>304</v>
+      </c>
+      <c r="J25" s="7">
         <v>1</v>
       </c>
       <c r="K25" s="7">
@@ -3160,14 +3172,14 @@
         <v>5</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M25" s="14">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
       <c r="N25" s="31">
         <f t="shared" si="2"/>
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="O25" s="9"/>
     </row>
@@ -3181,22 +3193,22 @@
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J26" s="7">
         <v>2</v>
@@ -3206,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M26" s="14">
         <v>0.255</v>
@@ -3226,36 +3238,41 @@
       <c r="C27" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D27" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="G27" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>253</v>
-      </c>
-      <c r="I27" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="J27" s="42">
+      <c r="D27" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="J27" s="35">
         <v>1</v>
       </c>
-      <c r="K27" s="45">
+      <c r="K27" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="31"/>
+        <v>305</v>
+      </c>
+      <c r="M27" s="14">
+        <v>0.41</v>
+      </c>
+      <c r="N27" s="31">
+        <f t="shared" si="2"/>
+        <v>2.0499999999999998</v>
+      </c>
       <c r="O27" s="34"/>
     </row>
     <row r="28" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3268,22 +3285,22 @@
         <v>4</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J28" s="7">
         <v>3</v>
@@ -3293,7 +3310,7 @@
         <v>15</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M28" s="14">
         <v>1.54E-2</v>
@@ -3314,22 +3331,22 @@
         <v>5</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J29" s="9">
         <v>1</v>
@@ -3339,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M29" s="14">
         <v>1.5</v>
@@ -3360,22 +3377,22 @@
         <v>6</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J30" s="7">
         <v>4</v>
@@ -3385,7 +3402,7 @@
         <v>20</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M30" s="14">
         <v>0.26900000000000002</v>
@@ -3396,97 +3413,96 @@
       </c>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>258</v>
+      <c r="C31" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J31" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L31" s="25" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M31" s="14">
-        <v>9.2999999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="N31" s="31">
         <f t="shared" si="2"/>
-        <v>2.3250000000000002</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B32) - ROW($B$2)</f>
         <v>30</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>7</v>
+        <v>322</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>159</v>
+        <v>320</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="J32" s="9">
-        <v>1</v>
+        <v>304</v>
+      </c>
+      <c r="J32" s="7">
+        <v>5</v>
       </c>
       <c r="K32" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L32" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M32" s="14">
-        <v>4.3280000000000003</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="N32" s="31">
         <f t="shared" si="2"/>
-        <v>21.64</v>
-      </c>
-      <c r="O32" s="9"/>
+        <v>2.3250000000000002</v>
+      </c>
+      <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3495,25 +3511,25 @@
         <v>31</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -3523,7 +3539,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M33" s="14">
         <v>6.8000000000000005E-2</v>
@@ -3534,38 +3550,47 @@
       </c>
       <c r="O33" s="7"/>
     </row>
-    <row r="34" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f>ROW(B34) - ROW($B$2)</f>
         <v>32</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="7">
+        <v>7</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G34" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="H34" s="38"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="38">
         <v>1</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L34" s="25"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="12" t="s">
-        <v>401</v>
-      </c>
+      <c r="L34" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="M34" s="46">
+        <v>2.98</v>
+      </c>
+      <c r="N34" s="47">
+        <f t="shared" si="2"/>
+        <v>14.9</v>
+      </c>
+      <c r="O34" s="12"/>
     </row>
     <row r="35" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3574,25 +3599,25 @@
         <v>33</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="J35" s="7">
         <v>1</v>
@@ -3602,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M35" s="14">
         <v>1.56</v>
@@ -3620,25 +3645,25 @@
         <v>34</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="J36" s="9">
         <v>1</v>
@@ -3648,7 +3673,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M36" s="14">
         <v>1.19</v>
@@ -3666,25 +3691,25 @@
         <v>35</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J37" s="7">
         <v>1</v>
@@ -3694,7 +3719,7 @@
         <v>5</v>
       </c>
       <c r="L37" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M37" s="14">
         <v>1.85</v>
@@ -3712,25 +3737,25 @@
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J38" s="9">
         <v>4</v>
@@ -3740,7 +3765,7 @@
         <v>20</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M38" s="14">
         <v>2.0799999999999999E-2</v>
@@ -3758,25 +3783,25 @@
         <v>37</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J39" s="7">
         <v>2</v>
@@ -3786,7 +3811,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M39" s="14">
         <v>2.1700000000000001E-2</v>
@@ -3804,25 +3829,25 @@
         <v>38</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J40" s="9">
         <v>1</v>
@@ -3832,7 +3857,7 @@
         <v>5</v>
       </c>
       <c r="L40" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M40" s="14">
         <v>2.1999999999999999E-2</v>
@@ -3850,25 +3875,25 @@
         <v>39</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J41" s="7">
         <v>1</v>
@@ -3878,7 +3903,7 @@
         <v>5</v>
       </c>
       <c r="L41" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M41" s="14">
         <v>3.1300000000000001E-2</v>
@@ -3896,25 +3921,25 @@
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J42" s="9">
         <v>1</v>
@@ -3924,7 +3949,7 @@
         <v>5</v>
       </c>
       <c r="L42" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M42" s="14">
         <v>1.0900000000000001</v>
@@ -3942,25 +3967,25 @@
         <v>41</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J43" s="7">
         <v>1</v>
@@ -3970,7 +3995,7 @@
         <v>5</v>
       </c>
       <c r="L43" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M43" s="14">
         <v>1.0900000000000001</v>
@@ -3988,25 +4013,25 @@
         <v>42</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J44" s="9">
         <v>2</v>
@@ -4016,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="L44" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M44" s="14">
         <v>0.2</v>
@@ -4034,25 +4059,25 @@
         <v>43</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="J45" s="9">
         <v>1</v>
@@ -4062,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="L45" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M45" s="14">
         <v>0.15</v>
@@ -4080,25 +4105,25 @@
         <v>44</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="J46" s="7">
         <v>1</v>
@@ -4108,7 +4133,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M46" s="14">
         <v>0.1</v>
@@ -4126,25 +4151,25 @@
         <v>45</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="J47" s="9">
         <v>1</v>
@@ -4154,7 +4179,7 @@
         <v>5</v>
       </c>
       <c r="L47" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M47" s="14">
         <v>0.15</v>
@@ -4172,25 +4197,25 @@
         <v>46</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="J48" s="7">
         <v>1</v>
@@ -4200,7 +4225,7 @@
         <v>5</v>
       </c>
       <c r="L48" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M48" s="14">
         <v>0.13</v>
@@ -4218,25 +4243,25 @@
         <v>47</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="J49" s="9">
         <v>1</v>
@@ -4246,7 +4271,7 @@
         <v>5</v>
       </c>
       <c r="L49" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M49" s="14">
         <v>0.64</v>
@@ -4264,25 +4289,25 @@
         <v>48</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="J50" s="7">
         <v>1</v>
@@ -4292,7 +4317,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M50" s="14">
         <v>0.15</v>
@@ -4310,25 +4335,25 @@
         <v>49</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="J51" s="9">
         <v>1</v>
@@ -4338,7 +4363,7 @@
         <v>5</v>
       </c>
       <c r="L51" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M51" s="14">
         <v>0.15</v>
@@ -4356,25 +4381,25 @@
         <v>50</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="J52" s="7">
         <v>1</v>
@@ -4384,7 +4409,7 @@
         <v>5</v>
       </c>
       <c r="L52" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M52" s="14">
         <v>0.15</v>
@@ -4402,25 +4427,25 @@
         <v>51</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J53" s="9">
         <v>1</v>
@@ -4430,7 +4455,7 @@
         <v>5</v>
       </c>
       <c r="L53" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M53" s="14">
         <v>0.15</v>
@@ -4448,25 +4473,25 @@
         <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J54" s="7">
         <v>1</v>
@@ -4476,7 +4501,7 @@
         <v>5</v>
       </c>
       <c r="L54" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M54" s="14">
         <v>0.1</v>
@@ -4494,25 +4519,25 @@
         <v>53</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="J55" s="9">
         <v>5</v>
@@ -4522,7 +4547,7 @@
         <v>25</v>
       </c>
       <c r="L55" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M55" s="14">
         <v>1.4999999999999999E-2</v>
@@ -4540,25 +4565,25 @@
         <v>54</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="J56" s="7">
         <v>1</v>
@@ -4568,7 +4593,7 @@
         <v>5</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M56" s="14">
         <v>0.1</v>
@@ -4586,25 +4611,25 @@
         <v>55</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="J57" s="9">
         <v>1</v>
@@ -4614,7 +4639,7 @@
         <v>5</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M57" s="14">
         <v>0.1</v>
@@ -4632,25 +4657,25 @@
         <v>56</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="J58" s="7">
         <v>1</v>
@@ -4660,7 +4685,7 @@
         <v>5</v>
       </c>
       <c r="L58" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M58" s="14">
         <v>1.4999999999999999E-2</v>
@@ -4678,25 +4703,25 @@
         <v>57</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J59" s="9">
         <v>1</v>
@@ -4706,7 +4731,7 @@
         <v>5</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M59" s="14">
         <v>0.1</v>
@@ -4724,25 +4749,25 @@
         <v>58</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J60" s="9">
         <v>1</v>
@@ -4752,7 +4777,7 @@
         <v>5</v>
       </c>
       <c r="L60" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M60" s="14">
         <v>0.1</v>
@@ -4770,25 +4795,25 @@
         <v>59</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J61" s="7">
         <v>6</v>
@@ -4798,7 +4823,7 @@
         <v>30</v>
       </c>
       <c r="L61" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M61" s="14">
         <v>1.4999999999999999E-2</v>
@@ -4816,25 +4841,25 @@
         <v>60</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J62" s="9">
         <v>2</v>
@@ -4844,7 +4869,7 @@
         <v>10</v>
       </c>
       <c r="L62" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M62" s="14">
         <v>1.9E-2</v>
@@ -4862,25 +4887,25 @@
         <v>61</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="J63" s="7">
         <v>1</v>
@@ -4890,7 +4915,7 @@
         <v>5</v>
       </c>
       <c r="L63" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M63" s="14">
         <v>0.1</v>
@@ -4908,25 +4933,25 @@
         <v>62</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="J64" s="9">
         <v>1</v>
@@ -4936,7 +4961,7 @@
         <v>5</v>
       </c>
       <c r="L64" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M64" s="14">
         <v>0.1</v>
@@ -4954,25 +4979,25 @@
         <v>63</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="J65" s="9">
         <v>1</v>
@@ -4982,7 +5007,7 @@
         <v>5</v>
       </c>
       <c r="L65" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M65" s="14">
         <v>0.14000000000000001</v>
@@ -5000,25 +5025,25 @@
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J66" s="9">
         <v>2</v>
@@ -5028,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="L66" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M66" s="14">
         <v>0.1</v>
@@ -5046,25 +5071,25 @@
         <v>65</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="J67" s="7">
         <v>1</v>
@@ -5074,7 +5099,7 @@
         <v>5</v>
       </c>
       <c r="L67" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M67" s="14">
         <v>0.1</v>
@@ -5092,25 +5117,25 @@
         <v>66</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="J68" s="7">
         <v>2</v>
@@ -5120,7 +5145,7 @@
         <v>10</v>
       </c>
       <c r="L68" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M68" s="14">
         <v>9.4030000000000002E-2</v>
@@ -5138,25 +5163,25 @@
         <v>67</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="J69" s="7">
         <v>2</v>
@@ -5166,7 +5191,7 @@
         <v>10</v>
       </c>
       <c r="L69" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M69" s="14">
         <v>1.0999999999999999E-2</v>
@@ -5184,25 +5209,25 @@
         <v>68</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="J70" s="9">
         <v>4</v>
@@ -5212,7 +5237,7 @@
         <v>20</v>
       </c>
       <c r="L70" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M70" s="14">
         <v>1.9E-2</v>
@@ -5230,25 +5255,25 @@
         <v>69</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J71" s="9">
         <v>4</v>
@@ -5258,7 +5283,7 @@
         <v>20</v>
       </c>
       <c r="L71" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M71" s="14">
         <v>0.16</v>
@@ -5276,25 +5301,25 @@
         <v>70</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="J72" s="7">
         <v>8</v>
@@ -5304,7 +5329,7 @@
         <v>40</v>
       </c>
       <c r="L72" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M72" s="14">
         <v>0.16</v>
@@ -5322,25 +5347,25 @@
         <v>71</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J73" s="9">
         <v>8</v>
@@ -5350,7 +5375,7 @@
         <v>40</v>
       </c>
       <c r="L73" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M73" s="14">
         <v>0.16</v>
@@ -5368,25 +5393,25 @@
         <v>72</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J74" s="9">
         <v>2</v>
@@ -5396,7 +5421,7 @@
         <v>10</v>
       </c>
       <c r="L74" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M74" s="14">
         <v>0.98299999999999998</v>
@@ -5414,25 +5439,25 @@
         <v>73</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G75" s="8">
         <v>760390015</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J75" s="7">
         <v>1</v>
@@ -5442,7 +5467,7 @@
         <v>5</v>
       </c>
       <c r="L75" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M75" s="14">
         <v>1.9</v>
@@ -5460,25 +5485,25 @@
         <v>74</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
@@ -5488,7 +5513,7 @@
         <v>5</v>
       </c>
       <c r="L76" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M76" s="14">
         <v>6.11</v>
@@ -5506,25 +5531,25 @@
         <v>75</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J77" s="7">
         <v>1</v>
@@ -5534,7 +5559,7 @@
         <v>5</v>
       </c>
       <c r="L77" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M77" s="14">
         <v>2.41</v>
@@ -5552,25 +5577,25 @@
         <v>76</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J78" s="9">
         <v>1</v>
@@ -5580,7 +5605,7 @@
         <v>5</v>
       </c>
       <c r="L78" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M78" s="14">
         <v>1.43</v>
@@ -5598,25 +5623,25 @@
         <v>77</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J79" s="7">
         <v>1</v>
@@ -5626,7 +5651,7 @@
         <v>5</v>
       </c>
       <c r="L79" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M79" s="14">
         <v>2.27</v>
@@ -5644,25 +5669,25 @@
         <v>78</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J80" s="9">
         <v>1</v>
@@ -5672,7 +5697,7 @@
         <v>5</v>
       </c>
       <c r="L80" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M80" s="14">
         <v>1.1599999999999999</v>
@@ -5690,25 +5715,25 @@
         <v>79</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J81" s="7">
         <v>1</v>
@@ -5718,7 +5743,7 @@
         <v>5</v>
       </c>
       <c r="L81" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M81" s="14">
         <v>4.66</v>
@@ -5736,25 +5761,25 @@
         <v>80</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J82" s="9">
         <v>1</v>
@@ -5764,7 +5789,7 @@
         <v>5</v>
       </c>
       <c r="L82" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M82" s="14">
         <v>3</v>
@@ -5782,25 +5807,25 @@
         <v>81</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J83" s="7">
         <v>1</v>
@@ -5810,7 +5835,7 @@
         <v>5</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M83" s="14">
         <v>2.6663999999999999</v>
@@ -5836,25 +5861,25 @@
         <v>82</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J84" s="9">
         <v>1</v>
@@ -5864,7 +5889,7 @@
         <v>5</v>
       </c>
       <c r="L84" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M84" s="14">
         <v>4.51</v>
@@ -5882,25 +5907,25 @@
         <v>83</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J85" s="7">
         <v>4</v>
@@ -5910,7 +5935,7 @@
         <v>20</v>
       </c>
       <c r="L85" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M85" s="14">
         <v>0.68</v>
@@ -5928,25 +5953,25 @@
         <v>84</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J86" s="9">
         <v>2</v>
@@ -5956,7 +5981,7 @@
         <v>10</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M86" s="14">
         <v>5.2880000000000003</v>
@@ -5974,25 +5999,25 @@
         <v>85</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J87" s="7">
         <v>1</v>
@@ -6002,7 +6027,7 @@
         <v>5</v>
       </c>
       <c r="L87" s="25" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M87" s="14">
         <v>0.95</v>
@@ -6020,22 +6045,22 @@
         <v>86</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="9">
@@ -6046,7 +6071,7 @@
         <v>40</v>
       </c>
       <c r="L88" s="26" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M88" s="14">
         <v>2.98</v>
@@ -6064,23 +6089,23 @@
         <v>87</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="8" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J89" s="7">
         <v>1</v>
@@ -6089,7 +6114,7 @@
         <v>2</v>
       </c>
       <c r="L89" s="25" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M89" s="14">
         <v>16.989999999999998</v>
@@ -6107,25 +6132,25 @@
         <v>88</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J90" s="9">
         <v>1</v>
@@ -6135,7 +6160,7 @@
         <v>5</v>
       </c>
       <c r="L90" s="27" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M90" s="29">
         <v>0.73499999999999999</v>
@@ -6153,25 +6178,25 @@
         <v>89</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="H91" s="21" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J91" s="21">
         <v>1</v>
@@ -6181,7 +6206,7 @@
         <v>5</v>
       </c>
       <c r="L91" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M91" s="30">
         <v>1.2457</v>
@@ -6203,14 +6228,14 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
-      <c r="K92" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="L92" s="37"/>
-      <c r="M92" s="38"/>
+      <c r="K92" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="L92" s="41"/>
+      <c r="M92" s="42"/>
       <c r="N92" s="18">
-        <f>SUM(N35:N91)</f>
-        <v>464.59530000000007</v>
+        <f>SUM(N3:N91)</f>
+        <v>595.30830000000003</v>
       </c>
       <c r="O92" s="1"/>
     </row>
@@ -6225,14 +6250,14 @@
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
-      <c r="K93" s="39" t="s">
-        <v>322</v>
-      </c>
-      <c r="L93" s="40"/>
-      <c r="M93" s="41"/>
+      <c r="K93" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="L93" s="44"/>
+      <c r="M93" s="45"/>
       <c r="N93" s="17">
         <f>N92/5</f>
-        <v>92.919060000000016</v>
+        <v>119.06166</v>
       </c>
       <c r="O93" s="1"/>
     </row>
@@ -6265,77 +6290,78 @@
     <hyperlink ref="L22" r:id="rId17"/>
     <hyperlink ref="L23" r:id="rId18"/>
     <hyperlink ref="L24" r:id="rId19"/>
-    <hyperlink ref="L25" r:id="rId20"/>
-    <hyperlink ref="L26" r:id="rId21"/>
-    <hyperlink ref="L27" r:id="rId22"/>
-    <hyperlink ref="L29" r:id="rId23"/>
-    <hyperlink ref="L30" r:id="rId24"/>
-    <hyperlink ref="L32" r:id="rId25"/>
-    <hyperlink ref="L35" r:id="rId26"/>
-    <hyperlink ref="L36" r:id="rId27"/>
-    <hyperlink ref="L37" r:id="rId28"/>
-    <hyperlink ref="L42" r:id="rId29"/>
-    <hyperlink ref="L43" r:id="rId30"/>
-    <hyperlink ref="L44" r:id="rId31"/>
-    <hyperlink ref="L45" r:id="rId32"/>
-    <hyperlink ref="L46" r:id="rId33"/>
-    <hyperlink ref="L47" r:id="rId34"/>
-    <hyperlink ref="L48" r:id="rId35"/>
-    <hyperlink ref="L49" r:id="rId36"/>
-    <hyperlink ref="L50" r:id="rId37"/>
-    <hyperlink ref="L51" r:id="rId38"/>
-    <hyperlink ref="L52" r:id="rId39"/>
-    <hyperlink ref="L53" r:id="rId40"/>
-    <hyperlink ref="L54" r:id="rId41"/>
-    <hyperlink ref="L55" r:id="rId42"/>
-    <hyperlink ref="L56" r:id="rId43"/>
-    <hyperlink ref="L57" r:id="rId44"/>
-    <hyperlink ref="L58" r:id="rId45"/>
-    <hyperlink ref="L59" r:id="rId46"/>
-    <hyperlink ref="L60" r:id="rId47"/>
-    <hyperlink ref="L61" r:id="rId48"/>
-    <hyperlink ref="L62" r:id="rId49"/>
-    <hyperlink ref="L63" r:id="rId50"/>
-    <hyperlink ref="L64" r:id="rId51"/>
-    <hyperlink ref="L68" r:id="rId52"/>
-    <hyperlink ref="L66" r:id="rId53"/>
-    <hyperlink ref="L70" r:id="rId54"/>
-    <hyperlink ref="L74" r:id="rId55"/>
-    <hyperlink ref="L75" r:id="rId56"/>
-    <hyperlink ref="L76" r:id="rId57"/>
-    <hyperlink ref="L77" r:id="rId58"/>
-    <hyperlink ref="L78" r:id="rId59"/>
-    <hyperlink ref="L79" r:id="rId60"/>
-    <hyperlink ref="L80" r:id="rId61"/>
-    <hyperlink ref="L81" r:id="rId62"/>
-    <hyperlink ref="L82" r:id="rId63"/>
-    <hyperlink ref="L84" r:id="rId64"/>
-    <hyperlink ref="L85" r:id="rId65"/>
-    <hyperlink ref="L86" r:id="rId66"/>
-    <hyperlink ref="L87" r:id="rId67"/>
-    <hyperlink ref="L28" r:id="rId68"/>
-    <hyperlink ref="L33" r:id="rId69"/>
-    <hyperlink ref="L38" r:id="rId70"/>
-    <hyperlink ref="L39" r:id="rId71"/>
-    <hyperlink ref="L40" r:id="rId72"/>
-    <hyperlink ref="L41" r:id="rId73"/>
-    <hyperlink ref="L83" r:id="rId74"/>
-    <hyperlink ref="L31" r:id="rId75"/>
-    <hyperlink ref="L69" r:id="rId76"/>
-    <hyperlink ref="L65" r:id="rId77"/>
-    <hyperlink ref="L67" r:id="rId78"/>
-    <hyperlink ref="L91" r:id="rId79"/>
-    <hyperlink ref="L19" r:id="rId80"/>
-    <hyperlink ref="L20" r:id="rId81"/>
-    <hyperlink ref="L21" r:id="rId82"/>
-    <hyperlink ref="L71" r:id="rId83"/>
-    <hyperlink ref="L72" r:id="rId84"/>
-    <hyperlink ref="L73" r:id="rId85"/>
-    <hyperlink ref="L88" r:id="rId86"/>
-    <hyperlink ref="L89" r:id="rId87"/>
-    <hyperlink ref="L90" r:id="rId88"/>
+    <hyperlink ref="L26" r:id="rId20"/>
+    <hyperlink ref="L27" r:id="rId21"/>
+    <hyperlink ref="L29" r:id="rId22"/>
+    <hyperlink ref="L30" r:id="rId23"/>
+    <hyperlink ref="L35" r:id="rId24"/>
+    <hyperlink ref="L36" r:id="rId25"/>
+    <hyperlink ref="L37" r:id="rId26"/>
+    <hyperlink ref="L42" r:id="rId27"/>
+    <hyperlink ref="L43" r:id="rId28"/>
+    <hyperlink ref="L44" r:id="rId29"/>
+    <hyperlink ref="L45" r:id="rId30"/>
+    <hyperlink ref="L46" r:id="rId31"/>
+    <hyperlink ref="L47" r:id="rId32"/>
+    <hyperlink ref="L48" r:id="rId33"/>
+    <hyperlink ref="L49" r:id="rId34"/>
+    <hyperlink ref="L50" r:id="rId35"/>
+    <hyperlink ref="L51" r:id="rId36"/>
+    <hyperlink ref="L52" r:id="rId37"/>
+    <hyperlink ref="L53" r:id="rId38"/>
+    <hyperlink ref="L54" r:id="rId39"/>
+    <hyperlink ref="L55" r:id="rId40"/>
+    <hyperlink ref="L56" r:id="rId41"/>
+    <hyperlink ref="L57" r:id="rId42"/>
+    <hyperlink ref="L58" r:id="rId43"/>
+    <hyperlink ref="L59" r:id="rId44"/>
+    <hyperlink ref="L60" r:id="rId45"/>
+    <hyperlink ref="L61" r:id="rId46"/>
+    <hyperlink ref="L62" r:id="rId47"/>
+    <hyperlink ref="L63" r:id="rId48"/>
+    <hyperlink ref="L64" r:id="rId49"/>
+    <hyperlink ref="L68" r:id="rId50"/>
+    <hyperlink ref="L66" r:id="rId51"/>
+    <hyperlink ref="L70" r:id="rId52"/>
+    <hyperlink ref="L74" r:id="rId53"/>
+    <hyperlink ref="L75" r:id="rId54"/>
+    <hyperlink ref="L76" r:id="rId55"/>
+    <hyperlink ref="L77" r:id="rId56"/>
+    <hyperlink ref="L78" r:id="rId57"/>
+    <hyperlink ref="L79" r:id="rId58"/>
+    <hyperlink ref="L80" r:id="rId59"/>
+    <hyperlink ref="L81" r:id="rId60"/>
+    <hyperlink ref="L82" r:id="rId61"/>
+    <hyperlink ref="L84" r:id="rId62"/>
+    <hyperlink ref="L85" r:id="rId63"/>
+    <hyperlink ref="L86" r:id="rId64"/>
+    <hyperlink ref="L87" r:id="rId65"/>
+    <hyperlink ref="L28" r:id="rId66"/>
+    <hyperlink ref="L33" r:id="rId67"/>
+    <hyperlink ref="L38" r:id="rId68"/>
+    <hyperlink ref="L39" r:id="rId69"/>
+    <hyperlink ref="L40" r:id="rId70"/>
+    <hyperlink ref="L41" r:id="rId71"/>
+    <hyperlink ref="L83" r:id="rId72"/>
+    <hyperlink ref="L32" r:id="rId73"/>
+    <hyperlink ref="L69" r:id="rId74"/>
+    <hyperlink ref="L65" r:id="rId75"/>
+    <hyperlink ref="L67" r:id="rId76"/>
+    <hyperlink ref="L91" r:id="rId77"/>
+    <hyperlink ref="L19" r:id="rId78"/>
+    <hyperlink ref="L20" r:id="rId79"/>
+    <hyperlink ref="L21" r:id="rId80"/>
+    <hyperlink ref="L71" r:id="rId81"/>
+    <hyperlink ref="L72" r:id="rId82"/>
+    <hyperlink ref="L73" r:id="rId83"/>
+    <hyperlink ref="L88" r:id="rId84"/>
+    <hyperlink ref="L89" r:id="rId85"/>
+    <hyperlink ref="L90" r:id="rId86"/>
+    <hyperlink ref="L25" r:id="rId87"/>
+    <hyperlink ref="L31" r:id="rId88"/>
+    <hyperlink ref="L34" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId89"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId90"/>
 </worksheet>
 </file>